--- a/sample-data/GCIO_Portfolio_Master.xlsx
+++ b/sample-data/GCIO_Portfolio_Master.xlsx
@@ -8,13 +8,14 @@
     <sheet sheetId="2" name="Milestones" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Updates" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Risks" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Posture" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="687">
   <si>
     <t>Project ID</t>
   </si>
@@ -1889,6 +1890,192 @@
   </si>
   <si>
     <t>Integration dependency on legacy interface engine</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Last Assessed</t>
+  </si>
+  <si>
+    <t>Next Review</t>
+  </si>
+  <si>
+    <t>Open Findings</t>
+  </si>
+  <si>
+    <t>Critical Findings</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Identity &amp; Access Management</t>
+  </si>
+  <si>
+    <t>Privileged access recertification</t>
+  </si>
+  <si>
+    <t>Non-Compliant</t>
+  </si>
+  <si>
+    <t>CISO</t>
+  </si>
+  <si>
+    <t>Quarterly recertification overdue in three directorates; break-glass accounts not reviewed since March.</t>
+  </si>
+  <si>
+    <t>PRJ-3005</t>
+  </si>
+  <si>
+    <t>Vulnerability Management</t>
+  </si>
+  <si>
+    <t>Critical patch SLA (14 days)</t>
+  </si>
+  <si>
+    <t>Head of Infrastructure</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Server estate is inside SLA; the clinical device estate is not, and cannot be patched in-hours.</t>
+  </si>
+  <si>
+    <t>PRJ-3004</t>
+  </si>
+  <si>
+    <t>Network Security</t>
+  </si>
+  <si>
+    <t>Segmentation between clinical and corporate</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Network Lead</t>
+  </si>
+  <si>
+    <t>2026-11-01</t>
+  </si>
+  <si>
+    <t>Core segmentation complete; three legacy VLANs still flat pending the migration.</t>
+  </si>
+  <si>
+    <t>Endpoint Protection</t>
+  </si>
+  <si>
+    <t>EDR coverage and policy compliance</t>
+  </si>
+  <si>
+    <t>Head of Digital Workplace</t>
+  </si>
+  <si>
+    <t>2026-11-12</t>
+  </si>
+  <si>
+    <t>Coverage at 88% of managed endpoints; the gap is shared clinical workstations.</t>
+  </si>
+  <si>
+    <t>Data Protection</t>
+  </si>
+  <si>
+    <t>Encryption at rest and in transit</t>
+  </si>
+  <si>
+    <t>Compliant</t>
+  </si>
+  <si>
+    <t>Chief Data Officer</t>
+  </si>
+  <si>
+    <t>2027-01-20</t>
+  </si>
+  <si>
+    <t>Meets policy across all tier-1 systems.</t>
+  </si>
+  <si>
+    <t>Backup &amp; Recovery</t>
+  </si>
+  <si>
+    <t>Tested restore of tier-1 systems</t>
+  </si>
+  <si>
+    <t>2026-12-30</t>
+  </si>
+  <si>
+    <t>Last full restore test passed within the target window.</t>
+  </si>
+  <si>
+    <t>Security Monitoring</t>
+  </si>
+  <si>
+    <t>24x7 detection coverage</t>
+  </si>
+  <si>
+    <t>SOC Manager</t>
+  </si>
+  <si>
+    <t>2026-11-05</t>
+  </si>
+  <si>
+    <t>12x5 today; tier-2 analyst recruitment is behind plan, so out-of-hours relies on on-call.</t>
+  </si>
+  <si>
+    <t>Third-Party Risk</t>
+  </si>
+  <si>
+    <t>Supplier security assessments</t>
+  </si>
+  <si>
+    <t>Procurement Lead</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>Assessments complete for tier-1 suppliers only; tier-2 backlog is growing.</t>
+  </si>
+  <si>
+    <t>Awareness &amp; Training</t>
+  </si>
+  <si>
+    <t>Annual mandatory training completion</t>
+  </si>
+  <si>
+    <t>Head of People</t>
+  </si>
+  <si>
+    <t>2027-02-18</t>
+  </si>
+  <si>
+    <t>Completion above target for the second quarter running.</t>
+  </si>
+  <si>
+    <t>Incident Response</t>
+  </si>
+  <si>
+    <t>Tested IR plan and playbooks</t>
+  </si>
+  <si>
+    <t>Not Assessed</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>Scheduled for assessment after the SOC modernisation go-live.</t>
   </si>
 </sst>
 </file>
@@ -9575,4 +9762,444 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="60" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D2">
+        <v>0.52</v>
+      </c>
+      <c r="E2">
+        <v>0.95</v>
+      </c>
+      <c r="F2" t="s">
+        <v>637</v>
+      </c>
+      <c r="G2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2" t="s">
+        <v>638</v>
+      </c>
+      <c r="L2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D3">
+        <v>0.61</v>
+      </c>
+      <c r="E3">
+        <v>0.9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>642</v>
+      </c>
+      <c r="G3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3" t="s">
+        <v>643</v>
+      </c>
+      <c r="I3">
+        <v>27</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>644</v>
+      </c>
+      <c r="L3" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>646</v>
+      </c>
+      <c r="B4" t="s">
+        <v>647</v>
+      </c>
+      <c r="C4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D4">
+        <v>0.74</v>
+      </c>
+      <c r="E4">
+        <v>0.95</v>
+      </c>
+      <c r="F4" t="s">
+        <v>649</v>
+      </c>
+      <c r="G4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>651</v>
+      </c>
+      <c r="L4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B5" t="s">
+        <v>653</v>
+      </c>
+      <c r="C5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D5">
+        <v>0.88</v>
+      </c>
+      <c r="E5">
+        <v>0.98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" t="s">
+        <v>655</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>656</v>
+      </c>
+      <c r="L5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B6" t="s">
+        <v>658</v>
+      </c>
+      <c r="C6" t="s">
+        <v>659</v>
+      </c>
+      <c r="D6">
+        <v>0.96</v>
+      </c>
+      <c r="E6">
+        <v>0.95</v>
+      </c>
+      <c r="F6" t="s">
+        <v>660</v>
+      </c>
+      <c r="G6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H6" t="s">
+        <v>661</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>662</v>
+      </c>
+      <c r="L6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>663</v>
+      </c>
+      <c r="B7" t="s">
+        <v>664</v>
+      </c>
+      <c r="C7" t="s">
+        <v>659</v>
+      </c>
+      <c r="D7">
+        <v>0.93</v>
+      </c>
+      <c r="E7">
+        <v>0.9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>642</v>
+      </c>
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" t="s">
+        <v>665</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>666</v>
+      </c>
+      <c r="L7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>667</v>
+      </c>
+      <c r="B8" t="s">
+        <v>668</v>
+      </c>
+      <c r="C8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D8">
+        <v>0.7</v>
+      </c>
+      <c r="E8">
+        <v>0.95</v>
+      </c>
+      <c r="F8" t="s">
+        <v>669</v>
+      </c>
+      <c r="G8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" t="s">
+        <v>670</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>671</v>
+      </c>
+      <c r="L8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B9" t="s">
+        <v>673</v>
+      </c>
+      <c r="C9" t="s">
+        <v>648</v>
+      </c>
+      <c r="D9">
+        <v>0.66</v>
+      </c>
+      <c r="E9">
+        <v>0.85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>674</v>
+      </c>
+      <c r="G9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" t="s">
+        <v>675</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>676</v>
+      </c>
+      <c r="L9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>677</v>
+      </c>
+      <c r="B10" t="s">
+        <v>678</v>
+      </c>
+      <c r="C10" t="s">
+        <v>659</v>
+      </c>
+      <c r="D10">
+        <v>0.94</v>
+      </c>
+      <c r="E10">
+        <v>0.9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>679</v>
+      </c>
+      <c r="G10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" t="s">
+        <v>680</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>681</v>
+      </c>
+      <c r="L10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B11" t="s">
+        <v>683</v>
+      </c>
+      <c r="C11" t="s">
+        <v>684</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>669</v>
+      </c>
+      <c r="G11" t="s">
+        <v>240</v>
+      </c>
+      <c r="H11" t="s">
+        <v>685</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>686</v>
+      </c>
+      <c r="L11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>